--- a/data/performance/daily/signal_list_2026-08-18.xlsx
+++ b/data/performance/daily/signal_list_2026-08-18.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>7475</v>
       </c>
       <c r="D5" t="n">
-        <v>7700</v>
+        <v/>
       </c>
       <c r="E5" t="n">
         <v>7700</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>3.01</v>
+      <c r="F5" t="n">
+        <v>7700</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>3.01</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H5" s="4" t="n">
+        <v>3.01</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>2900</v>
       </c>
       <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
         <v>2930</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>2940</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>690</v>
       </c>
       <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
         <v>670</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>710</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>2.9</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-2.9</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>166</v>
       </c>
       <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
         <v>166</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>175</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>5.42</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>149</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>161</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>166</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>11.41</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>8.050000000000001</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>87</v>
       </c>
       <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
         <v>90</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>92</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>5.75</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>3.45</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>2800</v>
       </c>
       <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
         <v>2910</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>2930</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>4.64</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>3.93</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>1300</v>
       </c>
       <c r="D12" t="n">
-        <v>1320</v>
+        <v/>
       </c>
       <c r="E12" t="n">
         <v>1320</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>1.54</v>
+      <c r="F12" t="n">
+        <v>1320</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>1.54</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H12" s="4" t="n">
+        <v>1.54</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>134</v>
       </c>
       <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
         <v>133</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>136</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-0.75</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -976,33 +1009,36 @@
         <v>2540</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>2600</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>2670</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>5.12</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>2.36</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1023,33 +1059,36 @@
         <v>1005</v>
       </c>
       <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
         <v>1000</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>1010</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-0.5</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,33 +1109,36 @@
         <v>236</v>
       </c>
       <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
         <v>238</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>240</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>1.69</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1117,33 +1159,36 @@
         <v>1840</v>
       </c>
       <c r="D17" t="n">
+        <v/>
+      </c>
+      <c r="E17" t="n">
         <v>1865</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>1875</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1164,33 +1209,36 @@
         <v>464</v>
       </c>
       <c r="D18" t="n">
+        <v/>
+      </c>
+      <c r="E18" t="n">
         <v>418</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>474</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>2.16</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-9.91</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1211,33 +1259,36 @@
         <v>3890</v>
       </c>
       <c r="D19" t="n">
+        <v/>
+      </c>
+      <c r="E19" t="n">
         <v>3900</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>3960</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>1.8</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>0.26</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1258,33 +1309,36 @@
         <v>1510</v>
       </c>
       <c r="D20" t="n">
+        <v/>
+      </c>
+      <c r="E20" t="n">
         <v>1505</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>1510</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>-0.33</v>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1305,33 +1359,36 @@
         <v>870</v>
       </c>
       <c r="D21" t="n">
+        <v/>
+      </c>
+      <c r="E21" t="n">
         <v>885</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>925</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>6.32</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>1.72</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1352,33 +1409,36 @@
         <v>1075</v>
       </c>
       <c r="D22" t="n">
+        <v/>
+      </c>
+      <c r="E22" t="n">
         <v>1100</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>1110</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>3.26</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>2.33</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1399,33 +1459,36 @@
         <v>59</v>
       </c>
       <c r="D23" t="n">
+        <v/>
+      </c>
+      <c r="E23" t="n">
         <v>61</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>64</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>8.470000000000001</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>3.39</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1446,33 +1509,36 @@
         <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>55</v>
+        <v/>
       </c>
       <c r="E24" t="n">
         <v>55</v>
       </c>
-      <c r="F24" s="4" t="n">
-        <v>3.77</v>
+      <c r="F24" t="n">
+        <v>55</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>3.77</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H24" s="4" t="n">
+        <v>3.77</v>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1493,33 +1559,36 @@
         <v>113</v>
       </c>
       <c r="D25" t="n">
-        <v>115</v>
+        <v/>
       </c>
       <c r="E25" t="n">
         <v>115</v>
       </c>
-      <c r="F25" s="4" t="n">
-        <v>1.77</v>
+      <c r="F25" t="n">
+        <v>115</v>
       </c>
       <c r="G25" s="4" t="n">
         <v>1.77</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H25" s="4" t="n">
+        <v>1.77</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1540,33 +1609,36 @@
         <v>300</v>
       </c>
       <c r="D26" t="n">
+        <v/>
+      </c>
+      <c r="E26" t="n">
         <v>280</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>310</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>3.33</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-6.67</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1587,33 +1659,36 @@
         <v>260</v>
       </c>
       <c r="D27" t="n">
+        <v/>
+      </c>
+      <c r="E27" t="n">
         <v>260</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>280</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>7.69</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1634,33 +1709,36 @@
         <v>7650</v>
       </c>
       <c r="D28" t="n">
-        <v>9175</v>
+        <v/>
       </c>
       <c r="E28" t="n">
         <v>9175</v>
       </c>
-      <c r="F28" s="4" t="n">
-        <v>19.93</v>
+      <c r="F28" t="n">
+        <v>9175</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>19.93</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H28" s="4" t="n">
+        <v>19.93</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1681,33 +1759,36 @@
         <v>122</v>
       </c>
       <c r="D29" t="n">
+        <v/>
+      </c>
+      <c r="E29" t="n">
         <v>122</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>131</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>7.38</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1728,33 +1809,36 @@
         <v>9975</v>
       </c>
       <c r="D30" t="n">
+        <v/>
+      </c>
+      <c r="E30" t="n">
         <v>10400</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>10950</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>9.77</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>4.26</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1775,33 +1859,36 @@
         <v>195</v>
       </c>
       <c r="D31" t="n">
+        <v/>
+      </c>
+      <c r="E31" t="n">
         <v>181</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>208</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>6.67</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>-7.18</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1822,33 +1909,36 @@
         <v>1680</v>
       </c>
       <c r="D32" t="n">
+        <v/>
+      </c>
+      <c r="E32" t="n">
         <v>1675</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>1740</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>3.57</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1869,33 +1959,36 @@
         <v>620</v>
       </c>
       <c r="D33" t="n">
+        <v/>
+      </c>
+      <c r="E33" t="n">
         <v>635</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>650</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>4.84</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>2.42</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1916,33 +2009,36 @@
         <v>296</v>
       </c>
       <c r="D34" t="n">
-        <v>324</v>
+        <v/>
       </c>
       <c r="E34" t="n">
         <v>324</v>
       </c>
-      <c r="F34" s="4" t="n">
-        <v>9.460000000000001</v>
+      <c r="F34" t="n">
+        <v>324</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H34" s="4" t="n">
+        <v>9.460000000000001</v>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1963,33 +2059,36 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
+        <v/>
+      </c>
+      <c r="E35" t="n">
         <v>69</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>71</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>1.43</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>-1.43</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2010,33 +2109,36 @@
         <v>885</v>
       </c>
       <c r="D36" t="n">
+        <v/>
+      </c>
+      <c r="E36" t="n">
         <v>875</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>915</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>3.39</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>-1.13</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2057,33 +2159,36 @@
         <v>232</v>
       </c>
       <c r="D37" t="n">
+        <v/>
+      </c>
+      <c r="E37" t="n">
         <v>214</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>230</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>-0.86</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>-7.76</v>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="J37" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2104,33 +2209,36 @@
         <v>77</v>
       </c>
       <c r="D38" t="n">
+        <v/>
+      </c>
+      <c r="E38" t="n">
         <v>78</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>80</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>3.9</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2151,33 +2259,36 @@
         <v>120</v>
       </c>
       <c r="D39" t="n">
+        <v/>
+      </c>
+      <c r="E39" t="n">
         <v>127</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>130</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>8.33</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>5.83</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2198,33 +2309,36 @@
         <v>206</v>
       </c>
       <c r="D40" t="n">
+        <v/>
+      </c>
+      <c r="E40" t="n">
         <v>202</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>206</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>-1.94</v>
       </c>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2245,33 +2359,36 @@
         <v>232</v>
       </c>
       <c r="D41" t="n">
+        <v/>
+      </c>
+      <c r="E41" t="n">
         <v>238</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>246</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>6.03</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>2.59</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2292,33 +2409,36 @@
         <v>8725</v>
       </c>
       <c r="D42" t="n">
+        <v/>
+      </c>
+      <c r="E42" t="n">
         <v>8675</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>8725</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>-0.57</v>
       </c>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="J42" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2339,33 +2459,36 @@
         <v>2530</v>
       </c>
       <c r="D43" t="n">
-        <v>2570</v>
+        <v/>
       </c>
       <c r="E43" t="n">
         <v>2570</v>
       </c>
-      <c r="F43" s="4" t="n">
-        <v>1.58</v>
+      <c r="F43" t="n">
+        <v>2570</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>1.58</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H43" s="4" t="n">
+        <v>1.58</v>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2386,33 +2509,36 @@
         <v>99</v>
       </c>
       <c r="D44" t="n">
+        <v/>
+      </c>
+      <c r="E44" t="n">
         <v>108</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>110</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>11.11</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>9.09</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2429,7 +2555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2437,12 +2563,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2472,45 +2599,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2531,33 +2663,36 @@
         <v>920</v>
       </c>
       <c r="D5" t="n">
+        <v/>
+      </c>
+      <c r="E5" t="n">
         <v>915</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>935</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>1.63</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-0.54</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2578,33 +2713,36 @@
         <v>2610</v>
       </c>
       <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
         <v>3090</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>3260</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>24.9</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>18.39</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2625,33 +2763,36 @@
         <v>464</v>
       </c>
       <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
         <v>494</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>520</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>12.07</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>6.47</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2672,33 +2813,36 @@
         <v>690</v>
       </c>
       <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
         <v>670</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>710</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>2.9</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-2.9</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2719,33 +2863,36 @@
         <v>14400</v>
       </c>
       <c r="D9" t="n">
-        <v>17275</v>
+        <v/>
       </c>
       <c r="E9" t="n">
         <v>17275</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>19.97</v>
+      <c r="F9" t="n">
+        <v>17275</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>19.97</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H9" s="4" t="n">
+        <v>19.97</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2766,33 +2913,36 @@
         <v>2800</v>
       </c>
       <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
         <v>2910</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>2930</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>4.64</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>3.93</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2813,33 +2963,36 @@
         <v>76</v>
       </c>
       <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
         <v>75</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>80</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>5.26</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-1.32</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2860,33 +3013,36 @@
         <v>134</v>
       </c>
       <c r="D12" t="n">
+        <v/>
+      </c>
+      <c r="E12" t="n">
         <v>133</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>136</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-0.75</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2907,33 +3063,36 @@
         <v>2540</v>
       </c>
       <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
         <v>2600</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>2670</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>5.12</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>2.36</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2954,33 +3113,36 @@
         <v>150</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>148</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>152</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>1.33</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-1.33</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3001,33 +3163,36 @@
         <v>110</v>
       </c>
       <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
         <v>108</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>115</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>4.55</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-1.82</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3048,33 +3213,36 @@
         <v>464</v>
       </c>
       <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
         <v>418</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>474</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>2.16</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-9.91</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3095,33 +3263,36 @@
         <v>195</v>
       </c>
       <c r="D17" t="n">
+        <v/>
+      </c>
+      <c r="E17" t="n">
         <v>186</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>208</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>6.67</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-4.62</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3142,33 +3313,36 @@
         <v>1200</v>
       </c>
       <c r="D18" t="n">
+        <v/>
+      </c>
+      <c r="E18" t="n">
         <v>1370</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>1500</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>14.17</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3189,33 +3363,36 @@
         <v>2330</v>
       </c>
       <c r="D19" t="n">
+        <v/>
+      </c>
+      <c r="E19" t="n">
         <v>2300</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>2340</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>0.43</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-1.29</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3236,33 +3413,36 @@
         <v>870</v>
       </c>
       <c r="D20" t="n">
+        <v/>
+      </c>
+      <c r="E20" t="n">
         <v>885</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>925</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>6.32</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>1.72</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3283,33 +3463,36 @@
         <v>218</v>
       </c>
       <c r="D21" t="n">
+        <v/>
+      </c>
+      <c r="E21" t="n">
         <v>218</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>230</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3330,33 +3513,36 @@
         <v>53</v>
       </c>
       <c r="D22" t="n">
-        <v>55</v>
+        <v/>
       </c>
       <c r="E22" t="n">
         <v>55</v>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>3.77</v>
+      <c r="F22" t="n">
+        <v>55</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>3.77</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H22" s="4" t="n">
+        <v>3.77</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3377,33 +3563,36 @@
         <v>1390</v>
       </c>
       <c r="D23" t="n">
+        <v/>
+      </c>
+      <c r="E23" t="n">
         <v>1425</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>1460</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>5.04</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>2.52</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3424,33 +3613,36 @@
         <v>14150</v>
       </c>
       <c r="D24" t="n">
+        <v/>
+      </c>
+      <c r="E24" t="n">
         <v>13225</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>14100</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>-0.35</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>-6.54</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3471,33 +3663,36 @@
         <v>660</v>
       </c>
       <c r="D25" t="n">
+        <v/>
+      </c>
+      <c r="E25" t="n">
         <v>665</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>670</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>1.52</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>0.76</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3518,33 +3713,36 @@
         <v>300</v>
       </c>
       <c r="D26" t="n">
+        <v/>
+      </c>
+      <c r="E26" t="n">
         <v>280</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>310</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>3.33</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-6.67</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3565,33 +3763,36 @@
         <v>160</v>
       </c>
       <c r="D27" t="n">
+        <v/>
+      </c>
+      <c r="E27" t="n">
         <v>179</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>193</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>20.62</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>11.88</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3612,33 +3813,36 @@
         <v>102</v>
       </c>
       <c r="D28" t="n">
+        <v/>
+      </c>
+      <c r="E28" t="n">
         <v>100</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>109</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>6.86</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>-1.96</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3659,33 +3863,36 @@
         <v>1605</v>
       </c>
       <c r="D29" t="n">
+        <v/>
+      </c>
+      <c r="E29" t="n">
         <v>1810</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>2000</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>24.61</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>12.77</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3706,33 +3913,36 @@
         <v>318</v>
       </c>
       <c r="D30" t="n">
+        <v/>
+      </c>
+      <c r="E30" t="n">
         <v>312</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>328</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>3.14</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>-1.89</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3753,33 +3963,36 @@
         <v>260</v>
       </c>
       <c r="D31" t="n">
+        <v/>
+      </c>
+      <c r="E31" t="n">
         <v>260</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>280</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>7.69</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3800,33 +4013,36 @@
         <v>122</v>
       </c>
       <c r="D32" t="n">
+        <v/>
+      </c>
+      <c r="E32" t="n">
         <v>122</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>131</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>7.38</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3847,33 +4063,36 @@
         <v>2140</v>
       </c>
       <c r="D33" t="n">
-        <v>2070</v>
+        <v/>
       </c>
       <c r="E33" t="n">
         <v>2070</v>
       </c>
-      <c r="F33" s="4" t="n">
-        <v>-3.27</v>
+      <c r="F33" t="n">
+        <v>2070</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>-3.27</v>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H33" s="4" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="J33" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3894,33 +4113,36 @@
         <v>9975</v>
       </c>
       <c r="D34" t="n">
+        <v/>
+      </c>
+      <c r="E34" t="n">
         <v>10400</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>10950</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>9.77</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>4.26</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3941,33 +4163,36 @@
         <v>195</v>
       </c>
       <c r="D35" t="n">
+        <v/>
+      </c>
+      <c r="E35" t="n">
         <v>181</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>208</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>6.67</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>-7.18</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3988,33 +4213,36 @@
         <v>1680</v>
       </c>
       <c r="D36" t="n">
+        <v/>
+      </c>
+      <c r="E36" t="n">
         <v>1675</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>1740</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>3.57</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4035,33 +4263,36 @@
         <v>5400</v>
       </c>
       <c r="D37" t="n">
+        <v/>
+      </c>
+      <c r="E37" t="n">
         <v>5200</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>5625</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>4.17</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>-3.7</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4082,33 +4313,36 @@
         <v>620</v>
       </c>
       <c r="D38" t="n">
+        <v/>
+      </c>
+      <c r="E38" t="n">
         <v>635</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>650</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>4.84</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>2.42</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4129,33 +4363,36 @@
         <v>2010</v>
       </c>
       <c r="D39" t="n">
-        <v>2510</v>
+        <v/>
       </c>
       <c r="E39" t="n">
         <v>2510</v>
       </c>
-      <c r="F39" s="4" t="n">
-        <v>24.88</v>
+      <c r="F39" t="n">
+        <v>2510</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>24.88</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H39" s="4" t="n">
+        <v>24.88</v>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4176,33 +4413,36 @@
         <v>74</v>
       </c>
       <c r="D40" t="n">
+        <v/>
+      </c>
+      <c r="E40" t="n">
         <v>72</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>77</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>4.05</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>-2.7</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4223,33 +4463,36 @@
         <v>71</v>
       </c>
       <c r="D41" t="n">
+        <v/>
+      </c>
+      <c r="E41" t="n">
         <v>77</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>82</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>15.49</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4270,33 +4513,36 @@
         <v>80</v>
       </c>
       <c r="D42" t="n">
+        <v/>
+      </c>
+      <c r="E42" t="n">
         <v>80</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>86</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>7.5</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4317,33 +4563,36 @@
         <v>825</v>
       </c>
       <c r="D43" t="n">
+        <v/>
+      </c>
+      <c r="E43" t="n">
         <v>840</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>870</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="G43" s="4" t="n">
         <v>5.45</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>1.82</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4364,33 +4613,36 @@
         <v>78</v>
       </c>
       <c r="D44" t="n">
+        <v/>
+      </c>
+      <c r="E44" t="n">
         <v>78</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>81</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>3.85</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4411,33 +4663,36 @@
         <v>210</v>
       </c>
       <c r="D45" t="n">
-        <v>262</v>
+        <v/>
       </c>
       <c r="E45" t="n">
         <v>262</v>
       </c>
-      <c r="F45" s="4" t="n">
-        <v>24.76</v>
+      <c r="F45" t="n">
+        <v>262</v>
       </c>
       <c r="G45" s="4" t="n">
         <v>24.76</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H45" s="4" t="n">
+        <v>24.76</v>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4458,33 +4713,36 @@
         <v>120</v>
       </c>
       <c r="D46" t="n">
+        <v/>
+      </c>
+      <c r="E46" t="n">
         <v>127</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>130</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="G46" s="4" t="n">
         <v>8.33</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>5.83</v>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4505,33 +4763,36 @@
         <v>232</v>
       </c>
       <c r="D47" t="n">
+        <v/>
+      </c>
+      <c r="E47" t="n">
         <v>238</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>246</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>6.03</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>2.59</v>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4552,33 +4813,36 @@
         <v>1790</v>
       </c>
       <c r="D48" t="n">
+        <v/>
+      </c>
+      <c r="E48" t="n">
         <v>1755</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>1875</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="G48" s="4" t="n">
         <v>4.75</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>-1.96</v>
       </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4599,33 +4863,36 @@
         <v>294</v>
       </c>
       <c r="D49" t="n">
+        <v/>
+      </c>
+      <c r="E49" t="n">
         <v>326</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>356</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="G49" s="4" t="n">
         <v>21.09</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>10.88</v>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4646,33 +4913,36 @@
         <v>99</v>
       </c>
       <c r="D50" t="n">
+        <v/>
+      </c>
+      <c r="E50" t="n">
         <v>108</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>110</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>11.11</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <v>9.09</v>
       </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-08-18.xlsx
+++ b/data/performance/daily/signal_list_2026-08-18.xlsx
@@ -559,7 +559,7 @@
         <v>7475</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>7475</v>
       </c>
       <c r="E5" t="n">
         <v>7700</v>
@@ -609,7 +609,7 @@
         <v>2900</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>2940</v>
       </c>
       <c r="E6" t="n">
         <v>2930</v>
@@ -659,7 +659,7 @@
         <v>690</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>690</v>
       </c>
       <c r="E7" t="n">
         <v>670</v>
@@ -709,7 +709,7 @@
         <v>166</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>165</v>
       </c>
       <c r="E8" t="n">
         <v>166</v>
@@ -759,7 +759,7 @@
         <v>149</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>149</v>
       </c>
       <c r="E9" t="n">
         <v>161</v>
@@ -809,7 +809,7 @@
         <v>87</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>88</v>
       </c>
       <c r="E10" t="n">
         <v>90</v>
@@ -859,7 +859,7 @@
         <v>2800</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>2840</v>
       </c>
       <c r="E11" t="n">
         <v>2910</v>
@@ -909,7 +909,7 @@
         <v>1300</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>1310</v>
       </c>
       <c r="E12" t="n">
         <v>1320</v>
@@ -959,7 +959,7 @@
         <v>134</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>133</v>
       </c>
       <c r="E13" t="n">
         <v>133</v>
@@ -1009,7 +1009,7 @@
         <v>2540</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>2600</v>
       </c>
       <c r="E14" t="n">
         <v>2600</v>
@@ -1059,7 +1059,7 @@
         <v>1005</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>1005</v>
       </c>
       <c r="E15" t="n">
         <v>1000</v>
@@ -1109,7 +1109,7 @@
         <v>236</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>240</v>
       </c>
       <c r="E16" t="n">
         <v>238</v>
@@ -1159,7 +1159,7 @@
         <v>1840</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>1840</v>
       </c>
       <c r="E17" t="n">
         <v>1865</v>
@@ -1209,7 +1209,7 @@
         <v>464</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>466</v>
       </c>
       <c r="E18" t="n">
         <v>418</v>
@@ -1259,7 +1259,7 @@
         <v>3890</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>3920</v>
       </c>
       <c r="E19" t="n">
         <v>3900</v>
@@ -1309,7 +1309,7 @@
         <v>1510</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>1510</v>
       </c>
       <c r="E20" t="n">
         <v>1505</v>
@@ -1359,7 +1359,7 @@
         <v>870</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>890</v>
       </c>
       <c r="E21" t="n">
         <v>885</v>
@@ -1409,7 +1409,7 @@
         <v>1075</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>1075</v>
       </c>
       <c r="E22" t="n">
         <v>1100</v>
@@ -1459,7 +1459,7 @@
         <v>59</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
         <v>61</v>
@@ -1509,7 +1509,7 @@
         <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>54</v>
       </c>
       <c r="E24" t="n">
         <v>55</v>
@@ -1559,7 +1559,7 @@
         <v>113</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>114</v>
       </c>
       <c r="E25" t="n">
         <v>115</v>
@@ -1609,7 +1609,7 @@
         <v>300</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>304</v>
       </c>
       <c r="E26" t="n">
         <v>280</v>
@@ -1659,7 +1659,7 @@
         <v>260</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>264</v>
       </c>
       <c r="E27" t="n">
         <v>260</v>
@@ -1709,7 +1709,7 @@
         <v>7650</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>9175</v>
       </c>
       <c r="E28" t="n">
         <v>9175</v>
@@ -1759,7 +1759,7 @@
         <v>122</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>124</v>
       </c>
       <c r="E29" t="n">
         <v>122</v>
@@ -1809,7 +1809,7 @@
         <v>9975</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>10500</v>
       </c>
       <c r="E30" t="n">
         <v>10400</v>
@@ -1859,7 +1859,7 @@
         <v>195</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>195</v>
       </c>
       <c r="E31" t="n">
         <v>181</v>
@@ -1909,7 +1909,7 @@
         <v>1680</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>1685</v>
       </c>
       <c r="E32" t="n">
         <v>1675</v>
@@ -1959,7 +1959,7 @@
         <v>620</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>615</v>
       </c>
       <c r="E33" t="n">
         <v>635</v>
@@ -2009,7 +2009,7 @@
         <v>296</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>300</v>
       </c>
       <c r="E34" t="n">
         <v>324</v>
@@ -2059,7 +2059,7 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>70</v>
       </c>
       <c r="E35" t="n">
         <v>69</v>
@@ -2109,7 +2109,7 @@
         <v>885</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>900</v>
       </c>
       <c r="E36" t="n">
         <v>875</v>
@@ -2159,7 +2159,7 @@
         <v>232</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>230</v>
       </c>
       <c r="E37" t="n">
         <v>214</v>
@@ -2209,7 +2209,7 @@
         <v>77</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>78</v>
       </c>
       <c r="E38" t="n">
         <v>78</v>
@@ -2259,7 +2259,7 @@
         <v>120</v>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>119</v>
       </c>
       <c r="E39" t="n">
         <v>127</v>
@@ -2309,7 +2309,7 @@
         <v>206</v>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>204</v>
       </c>
       <c r="E40" t="n">
         <v>202</v>
@@ -2359,7 +2359,7 @@
         <v>232</v>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>230</v>
       </c>
       <c r="E41" t="n">
         <v>238</v>
@@ -2409,7 +2409,7 @@
         <v>8725</v>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>8725</v>
       </c>
       <c r="E42" t="n">
         <v>8675</v>
@@ -2459,7 +2459,7 @@
         <v>2530</v>
       </c>
       <c r="D43" t="n">
-        <v/>
+        <v>2530</v>
       </c>
       <c r="E43" t="n">
         <v>2570</v>
@@ -2509,7 +2509,7 @@
         <v>99</v>
       </c>
       <c r="D44" t="n">
-        <v/>
+        <v>102</v>
       </c>
       <c r="E44" t="n">
         <v>108</v>
@@ -2663,7 +2663,7 @@
         <v>920</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>920</v>
       </c>
       <c r="E5" t="n">
         <v>915</v>
@@ -2713,7 +2713,7 @@
         <v>2610</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>2540</v>
       </c>
       <c r="E6" t="n">
         <v>3090</v>
@@ -2763,7 +2763,7 @@
         <v>464</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>460.78</v>
       </c>
       <c r="E7" t="n">
         <v>494</v>
@@ -2813,7 +2813,7 @@
         <v>690</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>690</v>
       </c>
       <c r="E8" t="n">
         <v>670</v>
@@ -2863,7 +2863,7 @@
         <v>14400</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>15500</v>
       </c>
       <c r="E9" t="n">
         <v>17275</v>
@@ -2913,7 +2913,7 @@
         <v>2800</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>2840</v>
       </c>
       <c r="E10" t="n">
         <v>2910</v>
@@ -2963,7 +2963,7 @@
         <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>77</v>
       </c>
       <c r="E11" t="n">
         <v>75</v>
@@ -3013,7 +3013,7 @@
         <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>133</v>
       </c>
       <c r="E12" t="n">
         <v>133</v>
@@ -3063,7 +3063,7 @@
         <v>2540</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>2600</v>
       </c>
       <c r="E13" t="n">
         <v>2600</v>
@@ -3113,7 +3113,7 @@
         <v>150</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>150</v>
       </c>
       <c r="E14" t="n">
         <v>148</v>
@@ -3163,7 +3163,7 @@
         <v>110</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>110</v>
       </c>
       <c r="E15" t="n">
         <v>108</v>
@@ -3213,7 +3213,7 @@
         <v>464</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>466</v>
       </c>
       <c r="E16" t="n">
         <v>418</v>
@@ -3263,7 +3263,7 @@
         <v>195</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>200</v>
       </c>
       <c r="E17" t="n">
         <v>186</v>
@@ -3313,7 +3313,7 @@
         <v>1200</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>1020</v>
       </c>
       <c r="E18" t="n">
         <v>1370</v>
@@ -3363,7 +3363,7 @@
         <v>2330</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>2330</v>
       </c>
       <c r="E19" t="n">
         <v>2300</v>
@@ -3413,7 +3413,7 @@
         <v>870</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>890</v>
       </c>
       <c r="E20" t="n">
         <v>885</v>
@@ -3463,7 +3463,7 @@
         <v>218</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>228</v>
       </c>
       <c r="E21" t="n">
         <v>218</v>
@@ -3513,7 +3513,7 @@
         <v>53</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>54</v>
       </c>
       <c r="E22" t="n">
         <v>55</v>
@@ -3563,7 +3563,7 @@
         <v>1390</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>1390</v>
       </c>
       <c r="E23" t="n">
         <v>1425</v>
@@ -3613,7 +3613,7 @@
         <v>14150</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>14000</v>
       </c>
       <c r="E24" t="n">
         <v>13225</v>
@@ -3663,7 +3663,7 @@
         <v>660</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>660</v>
       </c>
       <c r="E25" t="n">
         <v>665</v>
@@ -3713,7 +3713,7 @@
         <v>300</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>304</v>
       </c>
       <c r="E26" t="n">
         <v>280</v>
@@ -3763,7 +3763,7 @@
         <v>160</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>160</v>
       </c>
       <c r="E27" t="n">
         <v>179</v>
@@ -3813,7 +3813,7 @@
         <v>102</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>103</v>
       </c>
       <c r="E28" t="n">
         <v>100</v>
@@ -3863,7 +3863,7 @@
         <v>1605</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>1645</v>
       </c>
       <c r="E29" t="n">
         <v>1810</v>
@@ -3913,7 +3913,7 @@
         <v>318</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>328</v>
       </c>
       <c r="E30" t="n">
         <v>312</v>
@@ -3963,7 +3963,7 @@
         <v>260</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>264</v>
       </c>
       <c r="E31" t="n">
         <v>260</v>
@@ -4013,7 +4013,7 @@
         <v>122</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>124</v>
       </c>
       <c r="E32" t="n">
         <v>122</v>
@@ -4063,7 +4063,7 @@
         <v>2140</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>1960</v>
       </c>
       <c r="E33" t="n">
         <v>2070</v>
@@ -4113,7 +4113,7 @@
         <v>9975</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>10500</v>
       </c>
       <c r="E34" t="n">
         <v>10400</v>
@@ -4163,7 +4163,7 @@
         <v>195</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>195</v>
       </c>
       <c r="E35" t="n">
         <v>181</v>
@@ -4213,7 +4213,7 @@
         <v>1680</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>1685</v>
       </c>
       <c r="E36" t="n">
         <v>1675</v>
@@ -4263,7 +4263,7 @@
         <v>5400</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>5525</v>
       </c>
       <c r="E37" t="n">
         <v>5200</v>
@@ -4313,7 +4313,7 @@
         <v>620</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>615</v>
       </c>
       <c r="E38" t="n">
         <v>635</v>
@@ -4363,7 +4363,7 @@
         <v>2010</v>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>2170</v>
       </c>
       <c r="E39" t="n">
         <v>2510</v>
@@ -4413,7 +4413,7 @@
         <v>74</v>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>77</v>
       </c>
       <c r="E40" t="n">
         <v>72</v>
@@ -4463,7 +4463,7 @@
         <v>71</v>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>71</v>
       </c>
       <c r="E41" t="n">
         <v>77</v>
@@ -4513,7 +4513,7 @@
         <v>80</v>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>80</v>
       </c>
       <c r="E42" t="n">
         <v>80</v>
@@ -4563,7 +4563,7 @@
         <v>825</v>
       </c>
       <c r="D43" t="n">
-        <v/>
+        <v>840</v>
       </c>
       <c r="E43" t="n">
         <v>840</v>
@@ -4613,7 +4613,7 @@
         <v>78</v>
       </c>
       <c r="D44" t="n">
-        <v/>
+        <v>80</v>
       </c>
       <c r="E44" t="n">
         <v>78</v>
@@ -4663,7 +4663,7 @@
         <v>210</v>
       </c>
       <c r="D45" t="n">
-        <v/>
+        <v>228</v>
       </c>
       <c r="E45" t="n">
         <v>262</v>
@@ -4713,7 +4713,7 @@
         <v>120</v>
       </c>
       <c r="D46" t="n">
-        <v/>
+        <v>119</v>
       </c>
       <c r="E46" t="n">
         <v>127</v>
@@ -4763,7 +4763,7 @@
         <v>232</v>
       </c>
       <c r="D47" t="n">
-        <v/>
+        <v>230</v>
       </c>
       <c r="E47" t="n">
         <v>238</v>
@@ -4813,7 +4813,7 @@
         <v>1790</v>
       </c>
       <c r="D48" t="n">
-        <v/>
+        <v>1795</v>
       </c>
       <c r="E48" t="n">
         <v>1755</v>
@@ -4863,7 +4863,7 @@
         <v>294</v>
       </c>
       <c r="D49" t="n">
-        <v/>
+        <v>304</v>
       </c>
       <c r="E49" t="n">
         <v>326</v>
@@ -4913,7 +4913,7 @@
         <v>99</v>
       </c>
       <c r="D50" t="n">
-        <v/>
+        <v>102</v>
       </c>
       <c r="E50" t="n">
         <v>108</v>
